--- a/burndown_Bas (1).xlsx
+++ b/burndown_Bas (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lamia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B79D061-D604-41EC-8EFB-9A3151721329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CC3503-BA24-40D5-ABD1-0E237A65ECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>Taak</t>
   </si>
@@ -78,24 +78,9 @@
     <t>Repository maken</t>
   </si>
   <si>
-    <t>US 1</t>
-  </si>
-  <si>
-    <t>US 2</t>
-  </si>
-  <si>
-    <t>US 3</t>
-  </si>
-  <si>
-    <t>US 4</t>
-  </si>
-  <si>
     <t>US 5</t>
   </si>
   <si>
-    <t>US 6</t>
-  </si>
-  <si>
     <t>US 7</t>
   </si>
   <si>
@@ -105,9 +90,6 @@
     <t>US 9</t>
   </si>
   <si>
-    <t>US 10</t>
-  </si>
-  <si>
     <t>US 11</t>
   </si>
   <si>
@@ -117,9 +99,6 @@
     <t>US 13</t>
   </si>
   <si>
-    <t>US 14</t>
-  </si>
-  <si>
     <t>ERD</t>
   </si>
   <si>
@@ -220,6 +199,30 @@
   </si>
   <si>
     <t>Insert klant</t>
+  </si>
+  <si>
+    <t>US 1 Database maken</t>
+  </si>
+  <si>
+    <t>US 2 Klant toevoegen</t>
+  </si>
+  <si>
+    <t>US 3 Klant CRUD</t>
+  </si>
+  <si>
+    <t>Coderen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 4 </t>
+  </si>
+  <si>
+    <t>US 6 artikel CRUD</t>
+  </si>
+  <si>
+    <t>US 10 Verkooporder CRUD</t>
+  </si>
+  <si>
+    <t>US 14 Orderstatus</t>
   </si>
 </sst>
 </file>
@@ -527,7 +530,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>BurndownChart!$A$49</c:f>
+              <c:f>BurndownChart!$A$52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -616,36 +619,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BurndownChart!$B$49:$J$49</c:f>
+              <c:f>BurndownChart!$B$52:$J$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>66</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>63</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -662,7 +665,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>BurndownChart!$A$50</c:f>
+              <c:f>BurndownChart!$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -751,33 +754,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BurndownChart!$B$50:$J$50</c:f>
+              <c:f>BurndownChart!$B$53:$J$53</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>66</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>57.75</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49.5</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.25</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.75</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16.5</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.25</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1586,7 +1589,7 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>44449</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1932,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8170B0-2E68-477D-80A9-FF8E7DC32F40}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -1946,28 +1949,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1999,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2010,7 +2013,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2022,13 +2025,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2076,7 +2079,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
@@ -2090,14 +2093,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -2108,14 +2113,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -2126,14 +2133,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2144,7 +2153,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
@@ -2158,7 +2167,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -2166,7 +2175,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -2176,15 +2185,15 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -2194,15 +2203,15 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -2211,40 +2220,40 @@
       <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1"/>
+      <c r="A15" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2</v>
-      </c>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -2253,7 +2262,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -2262,16 +2271,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -2280,7 +2289,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -2289,47 +2298,50 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>31</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1"/>
+      <c r="A20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="16"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="2"/>
+        <v>24</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="16"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="2"/>
@@ -2343,7 +2355,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
@@ -2352,19 +2364,18 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>31</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B24" s="1"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -2376,7 +2387,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
@@ -2384,16 +2395,16 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>31</v>
+      <c r="F25" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
-        <v>44</v>
+      <c r="A26" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
@@ -2401,25 +2412,24 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="16"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2427,145 +2437,150 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="1"/>
+      <c r="A29" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="1"/>
+      <c r="A31" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="16"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
+      <c r="A32" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="G32" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="16"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="1"/>
+      <c r="A33" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="16"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2</v>
-      </c>
+      <c r="A34" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="1"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="G34" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
       <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
       <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="1"/>
+      <c r="A35" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2</v>
+      </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
       <c r="J35" s="16"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
+      <c r="A36" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
       <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1">
         <v>2</v>
@@ -2573,141 +2588,138 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="G37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="2"/>
       <c r="J37" s="16"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1">
-        <v>2</v>
-      </c>
+      <c r="A38" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="1"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="16"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="1"/>
+      <c r="A39" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1">
+        <v>2</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
+      <c r="H39" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J39" s="16"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J40" s="16"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="1"/>
+      <c r="A41" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J41" s="16"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2</v>
-      </c>
+      <c r="A42" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="1"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="J42" s="16"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B43" s="1"/>
+      <c r="A43" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2</v>
+      </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J43" s="16"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="1">
-        <v>2</v>
-      </c>
+      <c r="A44" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="I44" s="2"/>
       <c r="J44" s="16"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1"/>
+      <c r="A45" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2</v>
+      </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="16" t="s">
-        <v>31</v>
+      <c r="I45" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2</v>
-      </c>
+      <c r="A46" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="1"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -2718,28 +2730,27 @@
       <c r="J46" s="16"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="1"/>
+      <c r="A47" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="1">
+        <v>2</v>
+      </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1">
-        <v>2</v>
-      </c>
+      <c r="I47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2747,87 +2758,137 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="16"/>
+      <c r="J48" s="16" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="1">
+        <v>2</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="16"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="1">
+        <v>2</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="16"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="6">
-        <f>SUM(B3:B48)</f>
-        <v>66</v>
-      </c>
-      <c r="C49" s="7">
-        <f>B$49-SUM(C3:C48)</f>
-        <v>63</v>
-      </c>
-      <c r="D49" s="7">
-        <f>C$49-SUM(D3:D48)</f>
-        <v>63</v>
-      </c>
-      <c r="E49" s="7">
-        <f>D$49-SUM(E3:E48)</f>
-        <v>63</v>
-      </c>
-      <c r="F49" s="7">
-        <f>E$49-SUM(F3:F48)</f>
-        <v>63</v>
-      </c>
-      <c r="G49" s="7">
-        <f>F$49-SUM(G3:G48)</f>
-        <v>63</v>
-      </c>
-      <c r="H49" s="7">
-        <f>G$49-SUM(H3:H48)</f>
-        <v>63</v>
-      </c>
-      <c r="I49" s="7">
-        <f>H$49-SUM(I3:I48)</f>
-        <v>63</v>
-      </c>
-      <c r="J49" s="7">
-        <f>I$49-SUM(J3:J48)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="9">
-        <f>B49</f>
-        <v>66</v>
-      </c>
-      <c r="C50" s="10">
-        <f>B$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>57.75</v>
-      </c>
-      <c r="D50" s="10">
-        <f>C$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>49.5</v>
-      </c>
-      <c r="E50" s="10">
-        <f>D$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>41.25</v>
-      </c>
-      <c r="F50" s="10">
-        <f>E$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>33</v>
-      </c>
-      <c r="G50" s="10">
-        <f>F$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>24.75</v>
-      </c>
-      <c r="H50" s="10">
-        <f>G$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>16.5</v>
-      </c>
-      <c r="I50" s="10">
-        <f>H$50-$B$50/COUNTA($C$1:$J$1)</f>
-        <v>8.25</v>
-      </c>
-      <c r="J50" s="10">
-        <f>I$50-$B$50/COUNTA($C$1:$J$1)</f>
+      <c r="B52" s="6">
+        <f>SUM(B3:B51)</f>
+        <v>64</v>
+      </c>
+      <c r="C52" s="7">
+        <f>B$52-SUM(C3:C51)</f>
+        <v>54</v>
+      </c>
+      <c r="D52" s="7">
+        <f>C$52-SUM(D3:D51)</f>
+        <v>54</v>
+      </c>
+      <c r="E52" s="7">
+        <f>D$52-SUM(E3:E51)</f>
+        <v>54</v>
+      </c>
+      <c r="F52" s="7">
+        <f>E$52-SUM(F3:F51)</f>
+        <v>54</v>
+      </c>
+      <c r="G52" s="7">
+        <f>F$52-SUM(G3:G51)</f>
+        <v>54</v>
+      </c>
+      <c r="H52" s="7">
+        <f>G$52-SUM(H3:H51)</f>
+        <v>54</v>
+      </c>
+      <c r="I52" s="7">
+        <f>H$52-SUM(I3:I51)</f>
+        <v>54</v>
+      </c>
+      <c r="J52" s="7">
+        <f>I$52-SUM(J3:J51)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="9">
+        <f>B52</f>
+        <v>64</v>
+      </c>
+      <c r="C53" s="10">
+        <f>B$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>56</v>
+      </c>
+      <c r="D53" s="10">
+        <f>C$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>48</v>
+      </c>
+      <c r="E53" s="10">
+        <f>D$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>40</v>
+      </c>
+      <c r="F53" s="10">
+        <f>E$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>32</v>
+      </c>
+      <c r="G53" s="10">
+        <f>F$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>24</v>
+      </c>
+      <c r="H53" s="10">
+        <f>G$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>16</v>
+      </c>
+      <c r="I53" s="10">
+        <f>H$53-$B$53/COUNTA($C$1:$J$1)</f>
+        <v>8</v>
+      </c>
+      <c r="J53" s="10">
+        <f>I$53-$B$53/COUNTA($C$1:$J$1)</f>
         <v>0</v>
       </c>
     </row>
@@ -2840,6 +2901,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -3088,16 +3158,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3114,12 +3183,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/burndown_Bas (1).xlsx
+++ b/burndown_Bas (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lamia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CC3503-BA24-40D5-ABD1-0E237A65ECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A360F0-7A6D-4FD9-BB0F-6D5E0146251A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>Taak</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>US 14 Orderstatus</t>
+  </si>
+  <si>
+    <t>wireframe</t>
   </si>
 </sst>
 </file>
@@ -624,31 +627,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>64</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -759,28 +762,28 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>64</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56</c:v>
+                  <c:v>54.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>48</c:v>
+                  <c:v>46.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40</c:v>
+                  <c:v>38.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24</c:v>
+                  <c:v>23.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16</c:v>
+                  <c:v>15.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>7.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2172,7 +2175,9 @@
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
         <v>24</v>
@@ -2226,7 +2231,9 @@
       <c r="B15" s="1">
         <v>3</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
         <v>24</v>
@@ -2258,7 +2265,9 @@
       <c r="B17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
@@ -2329,7 +2338,9 @@
       <c r="B21" s="1">
         <v>3</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
@@ -2360,7 +2371,9 @@
       <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
@@ -2392,7 +2405,9 @@
       <c r="B25" s="1">
         <v>2</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
@@ -2406,9 +2421,7 @@
       <c r="A26" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="1">
-        <v>2</v>
-      </c>
+      <c r="B26" s="1"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2425,7 +2438,9 @@
       <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -2524,7 +2539,9 @@
       <c r="B33" s="1">
         <v>2</v>
       </c>
-      <c r="C33" s="2"/>
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="G33" s="2" t="s">
@@ -2555,7 +2572,9 @@
       <c r="B35" s="1">
         <v>2</v>
       </c>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2">
+        <v>2</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="G35" s="2" t="s">
@@ -2599,7 +2618,9 @@
         <v>61</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="2"/>
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -2615,7 +2636,9 @@
       <c r="B39" s="1">
         <v>2</v>
       </c>
-      <c r="C39" s="2"/>
+      <c r="C39" s="2">
+        <v>2</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="G39" s="2"/>
@@ -2626,12 +2649,14 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
-      <c r="C40" s="2"/>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="G40" s="2"/>
@@ -2641,42 +2666,46 @@
       <c r="J40" s="16"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
-      </c>
+      <c r="A41" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="1"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="H41" s="2"/>
       <c r="J41" s="16"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="2"/>
+      <c r="A42" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J42" s="16"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="G43" s="2"/>
@@ -2816,39 +2845,39 @@
       </c>
       <c r="B52" s="6">
         <f>SUM(B3:B51)</f>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C52" s="7">
         <f>B$52-SUM(C3:C51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D52" s="7">
         <f>C$52-SUM(D3:D51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E52" s="7">
         <f>D$52-SUM(E3:E51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="F52" s="7">
         <f>E$52-SUM(F3:F51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G52" s="7">
         <f>F$52-SUM(G3:G51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H52" s="7">
         <f>G$52-SUM(H3:H51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="I52" s="7">
         <f>H$52-SUM(I3:I51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="J52" s="7">
         <f>I$52-SUM(J3:J51)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2857,35 +2886,35 @@
       </c>
       <c r="B53" s="9">
         <f>B52</f>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C53" s="10">
         <f>B$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>56</v>
+        <v>54.25</v>
       </c>
       <c r="D53" s="10">
         <f>C$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>48</v>
+        <v>46.5</v>
       </c>
       <c r="E53" s="10">
         <f>D$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>40</v>
+        <v>38.75</v>
       </c>
       <c r="F53" s="10">
         <f>E$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G53" s="10">
         <f>F$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>24</v>
+        <v>23.25</v>
       </c>
       <c r="H53" s="10">
         <f>G$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I53" s="10">
         <f>H$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="J53" s="10">
         <f>I$53-$B$53/COUNTA($C$1:$J$1)</f>
@@ -2901,15 +2930,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -3158,15 +3178,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3183,4 +3204,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/burndown_Bas (1).xlsx
+++ b/burndown_Bas (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lamia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A360F0-7A6D-4FD9-BB0F-6D5E0146251A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7D77C5-F467-4D83-BBB1-348569B4C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>Taak</t>
   </si>
@@ -533,7 +533,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>BurndownChart!$A$52</c:f>
+              <c:f>BurndownChart!$A$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -622,36 +622,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BurndownChart!$B$52:$J$52</c:f>
+              <c:f>BurndownChart!$B$54:$J$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>62</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -668,7 +668,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>BurndownChart!$A$53</c:f>
+              <c:f>BurndownChart!$A$55</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -757,33 +757,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BurndownChart!$B$53:$J$53</c:f>
+              <c:f>BurndownChart!$B$55:$J$55</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>62</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54.25</c:v>
+                  <c:v>57.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46.5</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38.75</c:v>
+                  <c:v>41.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23.25</c:v>
+                  <c:v>24.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.5</c:v>
+                  <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.75</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1585,15 +1585,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>377824</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>598161</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>174433</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>44449</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:colOff>264786</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>140388</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1938,7 +1938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8170B0-2E68-477D-80A9-FF8E7DC32F40}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2101,11 +2101,9 @@
       <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
         <v>3</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -2121,11 +2119,9 @@
       <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <v>2</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -2141,11 +2137,9 @@
       <c r="B10" s="1">
         <v>2</v>
       </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>24</v>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>2</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2175,12 +2169,10 @@
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2">
         <v>1</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -2231,12 +2223,10 @@
       <c r="B15" s="1">
         <v>3</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2">
         <v>3</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -2265,13 +2255,11 @@
       <c r="B17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
+      <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>24</v>
+      <c r="F17" s="2">
+        <v>2</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -2338,13 +2326,11 @@
       <c r="B21" s="1">
         <v>3</v>
       </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
+      <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
-        <v>24</v>
+      <c r="F21" s="2">
+        <v>3</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2371,13 +2357,11 @@
       <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2" t="s">
-        <v>24</v>
+      <c r="F23" s="2">
+        <v>2</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -2405,13 +2389,11 @@
       <c r="B25" s="1">
         <v>2</v>
       </c>
-      <c r="C25" s="2">
-        <v>2</v>
-      </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2" t="s">
-        <v>24</v>
+      <c r="F25" s="2">
+        <v>2</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -2438,13 +2420,11 @@
       <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="C27" s="2">
-        <v>2</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="G27" s="2" t="s">
-        <v>24</v>
+      <c r="G27" s="2">
+        <v>2</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2539,13 +2519,11 @@
       <c r="B33" s="1">
         <v>2</v>
       </c>
-      <c r="C33" s="2">
-        <v>2</v>
-      </c>
+      <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>24</v>
+      <c r="G33" s="2">
+        <v>2</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2572,13 +2550,11 @@
       <c r="B35" s="1">
         <v>2</v>
       </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>24</v>
+      <c r="G35" s="2">
+        <v>2</v>
       </c>
       <c r="H35" s="2"/>
       <c r="J35" s="16"/>
@@ -2607,8 +2583,8 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="G37" s="2" t="s">
-        <v>24</v>
+      <c r="G37" s="2">
+        <v>2</v>
       </c>
       <c r="H37" s="2"/>
       <c r="J37" s="16"/>
@@ -2618,9 +2594,7 @@
         <v>61</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="2">
-        <v>2</v>
-      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -2636,14 +2610,12 @@
       <c r="B39" s="1">
         <v>2</v>
       </c>
-      <c r="C39" s="2">
-        <v>2</v>
-      </c>
+      <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2" t="s">
-        <v>24</v>
+      <c r="H39" s="2">
+        <v>2</v>
       </c>
       <c r="J39" s="16"/>
     </row>
@@ -2654,14 +2626,12 @@
       <c r="B40" s="1">
         <v>1</v>
       </c>
-      <c r="C40" s="2">
-        <v>1</v>
-      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2" t="s">
-        <v>24</v>
+      <c r="H40" s="2">
+        <v>1</v>
       </c>
       <c r="J40" s="16"/>
     </row>
@@ -2685,14 +2655,12 @@
       <c r="B42" s="1">
         <v>2</v>
       </c>
-      <c r="C42" s="2">
-        <v>2</v>
-      </c>
+      <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
-        <v>24</v>
+      <c r="H42" s="2">
+        <v>2</v>
       </c>
       <c r="J42" s="16"/>
     </row>
@@ -2703,14 +2671,12 @@
       <c r="B43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
+      <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="2" t="s">
-        <v>24</v>
+      <c r="H43" s="2">
+        <v>1</v>
       </c>
       <c r="J43" s="16"/>
     </row>
@@ -2740,60 +2706,59 @@
       <c r="E45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="2" t="s">
-        <v>24</v>
+      <c r="I45" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" s="1"/>
+      <c r="A46" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="16"/>
+      <c r="I46" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2</v>
-      </c>
+      <c r="A47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="1"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="I47" s="2"/>
       <c r="J47" s="16"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="1"/>
+      <c r="A48" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="1">
+        <v>2</v>
+      </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="16" t="s">
-        <v>24</v>
+      <c r="I48" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1">
         <v>2</v>
@@ -2801,15 +2766,16 @@
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+      <c r="I49" s="2">
+        <v>2</v>
+      </c>
       <c r="J49" s="16"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="2"/>
@@ -2823,9 +2789,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" s="1">
         <v>2</v>
@@ -2840,84 +2806,116 @@
       <c r="J51" s="16"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="16"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="6">
-        <f>SUM(B3:B51)</f>
-        <v>62</v>
-      </c>
-      <c r="C52" s="7">
-        <f>B$52-SUM(C3:C51)</f>
-        <v>25</v>
-      </c>
-      <c r="D52" s="7">
-        <f>C$52-SUM(D3:D51)</f>
-        <v>25</v>
-      </c>
-      <c r="E52" s="7">
-        <f>D$52-SUM(E3:E51)</f>
-        <v>25</v>
-      </c>
-      <c r="F52" s="7">
-        <f>E$52-SUM(F3:F51)</f>
-        <v>25</v>
-      </c>
-      <c r="G52" s="7">
-        <f>F$52-SUM(G3:G51)</f>
-        <v>25</v>
-      </c>
-      <c r="H52" s="7">
-        <f>G$52-SUM(H3:H51)</f>
-        <v>25</v>
-      </c>
-      <c r="I52" s="7">
-        <f>H$52-SUM(I3:I51)</f>
-        <v>25</v>
-      </c>
-      <c r="J52" s="7">
-        <f>I$52-SUM(J3:J51)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="B54" s="6">
+        <f>SUM(B3:B53)</f>
+        <v>66</v>
+      </c>
+      <c r="C54" s="7">
+        <f t="shared" ref="C54:J54" si="0">B$54-SUM(C3:C53)</f>
+        <v>63</v>
+      </c>
+      <c r="D54" s="7">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="E54" s="7">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="F54" s="7">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B53" s="9">
-        <f>B52</f>
-        <v>62</v>
-      </c>
-      <c r="C53" s="10">
-        <f>B$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>54.25</v>
-      </c>
-      <c r="D53" s="10">
-        <f>C$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>46.5</v>
-      </c>
-      <c r="E53" s="10">
-        <f>D$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>38.75</v>
-      </c>
-      <c r="F53" s="10">
-        <f>E$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>31</v>
-      </c>
-      <c r="G53" s="10">
-        <f>F$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>23.25</v>
-      </c>
-      <c r="H53" s="10">
-        <f>G$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>15.5</v>
-      </c>
-      <c r="I53" s="10">
-        <f>H$53-$B$53/COUNTA($C$1:$J$1)</f>
-        <v>7.75</v>
-      </c>
-      <c r="J53" s="10">
-        <f>I$53-$B$53/COUNTA($C$1:$J$1)</f>
+      <c r="G54" s="7">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H54" s="7">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="J54" s="7">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="9">
+        <f>B54</f>
+        <v>66</v>
+      </c>
+      <c r="C55" s="10">
+        <f t="shared" ref="C55:J55" si="1">B$55-$B$55/COUNTA($C$1:$J$1)</f>
+        <v>57.75</v>
+      </c>
+      <c r="D55" s="10">
+        <f t="shared" si="1"/>
+        <v>49.5</v>
+      </c>
+      <c r="E55" s="10">
+        <f t="shared" si="1"/>
+        <v>41.25</v>
+      </c>
+      <c r="F55" s="10">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="G55" s="10">
+        <f t="shared" si="1"/>
+        <v>24.75</v>
+      </c>
+      <c r="H55" s="10">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="I55" s="10">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
+      </c>
+      <c r="J55" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2930,6 +2928,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -3178,16 +3185,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3204,12 +3210,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>